--- a/frontend/plantilla-tir.xlsx
+++ b/frontend/plantilla-tir.xlsx
@@ -70,7 +70,7 @@
     <t xml:space="preserve">Moneda: ARS o USD (elegir de la lista desplegable). Si es ARS, la página convierte a USD con el dólar CCL de esa fecha exacta. Si esa fecha cae fin de semana o feriado, usa el día hábil anterior más cercano.</t>
   </si>
   <si>
-    <t xml:space="preserve">Monto: el número solo, sin el símbolo $ ni puntos de miles. Ejemplo: 1000000, no $1.000.000.</t>
+    <t xml:space="preserve">Monto: podés escribirlo como número solo (1000000) o con formato de moneda ($1,000,000.00). Ambos funcionan.</t>
   </si>
   <si>
     <t xml:space="preserve">No cambies los nombres de las pestañas (Ingreso, Retiro, Cartera) ni los encabezados de las columnas.</t>

--- a/frontend/plantilla-tir.xlsx
+++ b/frontend/plantilla-tir.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t xml:space="preserve">Antifragil Inversiones - Plantilla de carga para cálculo de TIR</t>
   </si>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">3.</t>
   </si>
   <si>
-    <t xml:space="preserve">Completá la pestaña "Cartera" con el Valor Inicial (fecha desde la que arranca el cálculo) y el Valor Actual (hoy).</t>
+    <t xml:space="preserve">Completá la pestaña "Cartera" con el Valor Actual (hoy). El Valor Inicial es OPCIONAL: solo usalo si NO cargaste el historial completo de ingresos/retiros y querés arrancar desde una fecha intermedia.</t>
   </si>
   <si>
     <t xml:space="preserve">4.</t>
@@ -112,13 +112,16 @@
     <t xml:space="preserve">Reglas importantes:</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Esta pestaña debe tener SOLO estas dos filas (una Valor Inicial, una Valor Actual). No agregues más filas acá.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  Valor Inicial: valor de la cartera en la fecha desde la que querés que arranque el cálculo de la TIR.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  Valor Actual: valor de la cartera hoy, con la fecha de hoy.</t>
+    <t xml:space="preserve">•  Esta pestaña debe tener como máximo estas dos filas: Valor Inicial (opcional) y Valor Actual (obligatoria).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Valor Actual: obligatorio. Valor de la cartera hoy, con la fecha de hoy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Valor Inicial: OPCIONAL. Usalo solo si NO cargaste el historial completo de ingresos/retiros y querés arrancar el cálculo desde una fecha intermedia, tomando el valor que tenía la cartera ese día como si fuera una inversión inicial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  Si ya cargaste TODOS los ingresos y retiros desde el primer depósito real, NO agregues Valor Inicial: ya está representado por esos movimientos. Agregarlo de más cuenta esa plata dos veces y arruina el cálculo.</t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1136,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -1216,14 +1219,23 @@
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
     </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation allowBlank="true" error="Elegí ARS o USD" errorStyle="stop" errorTitle="Moneda inválida" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C6" type="list">
